--- a/database/event/2683/event_2683_evp_summary.xlsx
+++ b/database/event/2683/event_2683_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.6469</v>
+        <v>6.6097</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2284</v>
+        <v>3.7788</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8599</v>
+        <v>2.1894</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6469</v>
+        <v>6.6097</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1631</v>
+        <v>4.1259</v>
       </c>
       <c r="G2" t="n">
         <v>2.4838</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1631</v>
+        <v>4.1664</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1631</v>
+        <v>4.1664</v>
       </c>
       <c r="J2" t="n">
         <v>2.4838</v>
@@ -529,7 +529,7 @@
         <v>223</v>
       </c>
       <c r="M2" t="n">
-        <v>5.6469</v>
+        <v>6.6502</v>
       </c>
       <c r="N2" t="n">
         <v>356</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1477</v>
+        <v>6.3907</v>
       </c>
       <c r="C3" t="n">
-        <v>2.943</v>
+        <v>3.6536</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6582</v>
+        <v>2.1021</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1477</v>
+        <v>6.3907</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4629</v>
+        <v>3.7059</v>
       </c>
       <c r="G3" t="n">
         <v>2.6848</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4629</v>
+        <v>3.7059</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4629</v>
+        <v>3.7059</v>
       </c>
       <c r="J3" t="n">
         <v>2.6848</v>
@@ -575,7 +575,7 @@
         <v>119</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1477</v>
+        <v>6.390700000000001</v>
       </c>
       <c r="N3" t="n">
         <v>196</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3672</v>
+        <v>4.903</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4968</v>
+        <v>2.8031</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3429</v>
+        <v>1.5094</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3672</v>
+        <v>4.903</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9512</v>
+        <v>1.2805</v>
       </c>
       <c r="G4" t="n">
-        <v>3.416</v>
+        <v>3.6225</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9512</v>
+        <v>1.2805</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9512</v>
+        <v>1.2805</v>
       </c>
       <c r="J4" t="n">
-        <v>3.416</v>
+        <v>3.6225</v>
       </c>
       <c r="K4" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="L4" t="n">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3672</v>
+        <v>4.903</v>
       </c>
       <c r="N4" t="n">
-        <v>356</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3361</v>
+        <v>4.7327</v>
       </c>
       <c r="C5" t="n">
-        <v>2.479</v>
+        <v>2.7057</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3303</v>
+        <v>1.4416</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3361</v>
+        <v>4.7327</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7136</v>
+        <v>1.3167</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6225</v>
+        <v>3.416</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7136</v>
+        <v>1.3167</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7136</v>
+        <v>1.3167</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6225</v>
+        <v>3.416</v>
       </c>
       <c r="K5" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="L5" t="n">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3361</v>
+        <v>4.732699999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>313</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6">
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9888</v>
+        <v>4.5425</v>
       </c>
       <c r="C6" t="n">
-        <v>2.2804</v>
+        <v>2.597</v>
       </c>
       <c r="D6" t="n">
-        <v>1.19</v>
+        <v>1.3658</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9888</v>
+        <v>4.5425</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0804</v>
+        <v>2.6341</v>
       </c>
       <c r="G6" t="n">
         <v>1.9084</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0804</v>
+        <v>2.6341</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0804</v>
+        <v>2.6341</v>
       </c>
       <c r="J6" t="n">
         <v>1.9084</v>
@@ -713,7 +713,7 @@
         <v>194</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9888</v>
+        <v>4.5425</v>
       </c>
       <c r="N6" t="n">
         <v>313</v>
@@ -722,47 +722,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7933</v>
+        <v>4.4491</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1687</v>
+        <v>2.5436</v>
       </c>
       <c r="D7" t="n">
-        <v>1.111</v>
+        <v>1.3286</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7933</v>
+        <v>4.4491</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9655</v>
+        <v>3.7393</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8278</v>
+        <v>0.7098</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9655</v>
+        <v>3.7393</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9655</v>
+        <v>3.7393</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8278</v>
+        <v>0.7098</v>
       </c>
       <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
         <v>119</v>
       </c>
-      <c r="L7" t="n">
-        <v>194</v>
-      </c>
       <c r="M7" t="n">
-        <v>3.7933</v>
+        <v>4.4491</v>
       </c>
       <c r="N7" t="n">
-        <v>313</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2623</v>
+        <v>4.1799</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8651</v>
+        <v>2.3897</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8965</v>
+        <v>1.2214</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2623</v>
+        <v>4.1799</v>
       </c>
       <c r="F8" t="n">
-        <v>1.607</v>
+        <v>2.5246</v>
       </c>
       <c r="G8" t="n">
         <v>1.6553</v>
       </c>
       <c r="H8" t="n">
-        <v>1.607</v>
+        <v>2.5246</v>
       </c>
       <c r="I8" t="n">
-        <v>1.607</v>
+        <v>2.5246</v>
       </c>
       <c r="J8" t="n">
         <v>1.6553</v>
@@ -805,7 +805,7 @@
         <v>223</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2623</v>
+        <v>4.1799</v>
       </c>
       <c r="N8" t="n">
         <v>356</v>
@@ -814,231 +814,231 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9534</v>
+        <v>4.1564</v>
       </c>
       <c r="C9" t="n">
-        <v>1.6885</v>
+        <v>2.3762</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7717000000000001</v>
+        <v>1.212</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9534</v>
+        <v>4.1564</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2436</v>
+        <v>2.3286</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7098</v>
+        <v>1.8278</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2436</v>
+        <v>2.3286</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2436</v>
+        <v>2.3286</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7098</v>
+        <v>1.8278</v>
       </c>
       <c r="K9" t="n">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="L9" t="n">
-        <v>119</v>
+        <v>194</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9534</v>
+        <v>4.1564</v>
       </c>
       <c r="N9" t="n">
-        <v>196</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8378</v>
+        <v>3.975</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6224</v>
+        <v>2.2725</v>
       </c>
       <c r="D10" t="n">
-        <v>0.725</v>
+        <v>1.1397</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8378</v>
+        <v>3.975</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1848</v>
+        <v>3.8264</v>
       </c>
       <c r="G10" t="n">
-        <v>0.653</v>
+        <v>0.1486</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1848</v>
+        <v>3.8264</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1848</v>
+        <v>3.8264</v>
       </c>
       <c r="J10" t="n">
-        <v>0.653</v>
+        <v>0.1486</v>
       </c>
       <c r="K10" t="n">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="L10" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8378</v>
+        <v>3.975</v>
       </c>
       <c r="N10" t="n">
-        <v>183</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8356</v>
+        <v>3.6324</v>
       </c>
       <c r="C11" t="n">
-        <v>1.6211</v>
+        <v>2.0767</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7242</v>
+        <v>1.0032</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8356</v>
+        <v>3.6324</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0502</v>
+        <v>2.9794</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7854</v>
+        <v>0.653</v>
       </c>
       <c r="H11" t="n">
-        <v>2.0502</v>
+        <v>2.9794</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0502</v>
+        <v>2.9794</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7854</v>
+        <v>0.653</v>
       </c>
       <c r="K11" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="L11" t="n">
-        <v>141</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8356</v>
+        <v>3.6324</v>
       </c>
       <c r="N11" t="n">
-        <v>241</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5574</v>
+        <v>3.2943</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4621</v>
+        <v>1.8834</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6118</v>
+        <v>0.8685</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5574</v>
+        <v>3.2943</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4088</v>
+        <v>2.5089</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1486</v>
+        <v>0.7854</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4088</v>
+        <v>2.5089</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4088</v>
+        <v>2.5089</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1486</v>
+        <v>0.7854</v>
       </c>
       <c r="K12" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5574</v>
+        <v>3.2943</v>
       </c>
       <c r="N12" t="n">
-        <v>140</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5568</v>
+        <v>3.1248</v>
       </c>
       <c r="C13" t="n">
-        <v>1.4617</v>
+        <v>1.7865</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6115</v>
+        <v>0.801</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5568</v>
+        <v>3.1248</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3053</v>
+        <v>2.8148</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8621</v>
+        <v>0.31</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3053</v>
+        <v>2.8148</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3053</v>
+        <v>2.8148</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8621</v>
+        <v>0.31</v>
       </c>
       <c r="K13" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="L13" t="n">
-        <v>223</v>
+        <v>69</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5568</v>
+        <v>3.1248</v>
       </c>
       <c r="N13" t="n">
-        <v>356</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5339</v>
+        <v>2.9865</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4486</v>
+        <v>1.7074</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.7459</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5339</v>
+        <v>2.9865</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0505</v>
+        <v>1.5031</v>
       </c>
       <c r="G14" t="n">
         <v>1.4834</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0505</v>
+        <v>1.5031</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0505</v>
+        <v>1.5031</v>
       </c>
       <c r="J14" t="n">
         <v>1.4834</v>
@@ -1081,7 +1081,7 @@
         <v>82</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5339</v>
+        <v>2.9865</v>
       </c>
       <c r="N14" t="n">
         <v>192</v>
@@ -1090,403 +1090,403 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.1462</v>
+        <v>2.9085</v>
       </c>
       <c r="C15" t="n">
-        <v>1.227</v>
+        <v>1.6628</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4457</v>
+        <v>0.7148</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1462</v>
+        <v>2.9085</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9971</v>
+        <v>3.3179</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1491</v>
+        <v>-0.4094</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9971</v>
+        <v>3.3179</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9971</v>
+        <v>3.3179</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1491</v>
+        <v>-0.4094</v>
       </c>
       <c r="K15" t="n">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="L15" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1462</v>
+        <v>2.9085</v>
       </c>
       <c r="N15" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0664</v>
+        <v>2.5568</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1814</v>
+        <v>1.4617</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4134</v>
+        <v>0.5747</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0664</v>
+        <v>2.5568</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7026</v>
+        <v>-0.3053</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3638</v>
+        <v>2.8621</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7026</v>
+        <v>-0.3053</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7026</v>
+        <v>-0.3053</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3638</v>
+        <v>2.8621</v>
       </c>
       <c r="K16" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L16" t="n">
-        <v>141</v>
+        <v>223</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0664</v>
+        <v>2.5568</v>
       </c>
       <c r="N16" t="n">
-        <v>241</v>
+        <v>356</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.0554</v>
+        <v>2.5286</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1751</v>
+        <v>1.4456</v>
       </c>
       <c r="D17" t="n">
-        <v>0.409</v>
+        <v>0.5635</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0554</v>
+        <v>2.5286</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7454</v>
+        <v>3.1419</v>
       </c>
       <c r="G17" t="n">
-        <v>0.31</v>
+        <v>-0.6133</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7454</v>
+        <v>3.1419</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7454</v>
+        <v>3.1419</v>
       </c>
       <c r="J17" t="n">
-        <v>0.31</v>
+        <v>-0.6133</v>
       </c>
       <c r="K17" t="n">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="L17" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0554</v>
+        <v>2.5286</v>
       </c>
       <c r="N17" t="n">
-        <v>188</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8852</v>
+        <v>2.3733</v>
       </c>
       <c r="C18" t="n">
-        <v>1.0778</v>
+        <v>1.3568</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3402</v>
+        <v>0.5016</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8852</v>
+        <v>2.3733</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0984</v>
+        <v>2.3733</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7868000000000001</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0984</v>
+        <v>2.3733</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0984</v>
+        <v>2.3733</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7868000000000001</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="L18" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8852</v>
+        <v>2.3733</v>
       </c>
       <c r="N18" t="n">
-        <v>241</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.7667</v>
+        <v>2.3705</v>
       </c>
       <c r="C19" t="n">
-        <v>1.01</v>
+        <v>1.3552</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2923</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7667</v>
+        <v>2.3705</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8213</v>
+        <v>1.5837</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0546</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8213</v>
+        <v>1.5837</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8213</v>
+        <v>1.5837</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0546</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="L19" t="n">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7667</v>
+        <v>2.3705</v>
       </c>
       <c r="N19" t="n">
-        <v>140</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7371</v>
+        <v>2.3639</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9931</v>
+        <v>1.3515</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2804</v>
+        <v>0.4979</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7371</v>
+        <v>2.3639</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4114</v>
+        <v>1.2148</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3257</v>
+        <v>1.1491</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4114</v>
+        <v>1.2148</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4114</v>
+        <v>1.2148</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3257</v>
+        <v>1.1491</v>
       </c>
       <c r="K20" t="n">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="L20" t="n">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7371</v>
+        <v>2.3639</v>
       </c>
       <c r="N20" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4961</v>
+        <v>2.3215</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8552999999999999</v>
+        <v>1.3272</v>
       </c>
       <c r="D21" t="n">
-        <v>0.183</v>
+        <v>0.481</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4961</v>
+        <v>2.3215</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1094</v>
+        <v>1.9958</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6133</v>
+        <v>0.3257</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1094</v>
+        <v>1.9958</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1094</v>
+        <v>1.9958</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6133</v>
+        <v>0.3257</v>
       </c>
       <c r="K21" t="n">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="L21" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4961</v>
+        <v>2.3215</v>
       </c>
       <c r="N21" t="n">
-        <v>140</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.3601</v>
+        <v>2.239</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7776</v>
+        <v>1.28</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1281</v>
+        <v>0.4481</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3601</v>
+        <v>2.239</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0289</v>
+        <v>2.239</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6688</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0289</v>
+        <v>2.239</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0289</v>
+        <v>2.239</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6688</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="L22" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3601</v>
+        <v>2.239</v>
       </c>
       <c r="N22" t="n">
-        <v>183</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.3563</v>
+        <v>2.2339</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7754</v>
+        <v>1.2771</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1266</v>
+        <v>0.4461</v>
       </c>
       <c r="E23" t="n">
-        <v>1.3563</v>
+        <v>2.2339</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0544</v>
+        <v>2.2885</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.0546</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0544</v>
+        <v>2.2885</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0544</v>
+        <v>2.2885</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.0546</v>
       </c>
       <c r="K23" t="n">
         <v>64</v>
@@ -1495,7 +1495,7 @@
         <v>76</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3563</v>
+        <v>2.2339</v>
       </c>
       <c r="N23" t="n">
         <v>140</v>
@@ -1504,216 +1504,216 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3526</v>
+        <v>2.2072</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7733</v>
+        <v>1.2619</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1251</v>
+        <v>0.4354</v>
       </c>
       <c r="E24" t="n">
-        <v>1.3526</v>
+        <v>2.2072</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3526</v>
+        <v>2.3012</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.094</v>
       </c>
       <c r="H24" t="n">
-        <v>1.3526</v>
+        <v>2.3012</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3526</v>
+        <v>2.3012</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.094</v>
       </c>
       <c r="K24" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3526</v>
+        <v>2.2072</v>
       </c>
       <c r="N24" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.3495</v>
+        <v>2.2036</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7715</v>
+        <v>1.2598</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1238</v>
+        <v>0.434</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3495</v>
+        <v>2.2036</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3495</v>
+        <v>0.8398</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.3638</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3495</v>
+        <v>0.8398</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3495</v>
+        <v>0.8398</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1.3638</v>
       </c>
       <c r="K25" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="M25" t="n">
-        <v>1.3495</v>
+        <v>2.2036</v>
       </c>
       <c r="N25" t="n">
-        <v>112</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.3381</v>
+        <v>2.1227</v>
       </c>
       <c r="C26" t="n">
-        <v>0.765</v>
+        <v>1.2136</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1192</v>
+        <v>0.4018</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3381</v>
+        <v>2.1227</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4321</v>
+        <v>3.1227</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.094</v>
+        <v>-1</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4321</v>
+        <v>3.1227</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4321</v>
+        <v>3.1227</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.094</v>
+        <v>-1</v>
       </c>
       <c r="K26" t="n">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="L26" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3381</v>
+        <v>2.1227</v>
       </c>
       <c r="N26" t="n">
-        <v>140</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.2807</v>
+        <v>2.119</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7322</v>
+        <v>1.2114</v>
       </c>
       <c r="D27" t="n">
-        <v>0.096</v>
+        <v>0.4003</v>
       </c>
       <c r="E27" t="n">
-        <v>1.2807</v>
+        <v>2.119</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8932</v>
+        <v>2.119</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3875</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8932</v>
+        <v>2.119</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8932</v>
+        <v>2.119</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3875</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L27" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2807</v>
+        <v>2.119</v>
       </c>
       <c r="N27" t="n">
-        <v>188</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>draken</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.2433</v>
+        <v>1.7856</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7108</v>
+        <v>1.0208</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0809</v>
+        <v>0.2675</v>
       </c>
       <c r="E28" t="n">
-        <v>1.2433</v>
+        <v>1.7856</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2433</v>
+        <v>1.7856</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2433</v>
+        <v>1.7856</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2433</v>
+        <v>1.7856</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.2433</v>
+        <v>1.7856</v>
       </c>
       <c r="N28" t="n">
         <v>120</v>
@@ -1734,1090 +1734,1090 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.2414</v>
+        <v>1.783</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7097</v>
+        <v>1.0194</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0801</v>
+        <v>0.2664</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2414</v>
+        <v>1.783</v>
       </c>
       <c r="F29" t="n">
-        <v>1.6508</v>
+        <v>2.4811</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4094</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6508</v>
+        <v>2.4811</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6508</v>
+        <v>2.4811</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4094</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="L29" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2414</v>
+        <v>1.783</v>
       </c>
       <c r="N29" t="n">
-        <v>188</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.1978</v>
+        <v>1.7186</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6848</v>
+        <v>0.9825</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0625</v>
+        <v>0.2408</v>
       </c>
       <c r="E30" t="n">
-        <v>1.1978</v>
+        <v>1.7186</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1978</v>
+        <v>1.7186</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1978</v>
+        <v>1.7186</v>
       </c>
       <c r="I30" t="n">
-        <v>1.1978</v>
+        <v>1.7186</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1978</v>
+        <v>1.7186</v>
       </c>
       <c r="N30" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1522</v>
+        <v>1.6953</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6587</v>
+        <v>0.9692</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0441</v>
+        <v>0.2315</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1522</v>
+        <v>1.6953</v>
       </c>
       <c r="F31" t="n">
-        <v>1.1522</v>
+        <v>2.3641</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.6688</v>
       </c>
       <c r="H31" t="n">
-        <v>1.1522</v>
+        <v>2.3641</v>
       </c>
       <c r="I31" t="n">
-        <v>1.1522</v>
+        <v>2.3641</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.6688</v>
       </c>
       <c r="K31" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1522</v>
+        <v>1.6953</v>
       </c>
       <c r="N31" t="n">
-        <v>121</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1369</v>
+        <v>1.6952</v>
       </c>
       <c r="C32" t="n">
-        <v>0.65</v>
+        <v>0.9692</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0379</v>
+        <v>0.2315</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1369</v>
+        <v>1.6952</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0975</v>
+        <v>1.6952</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0394</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0975</v>
+        <v>1.6952</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0975</v>
+        <v>1.6952</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0394</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="L32" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1369</v>
+        <v>1.6952</v>
       </c>
       <c r="N32" t="n">
-        <v>183</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>draken</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1176</v>
+        <v>1.4809</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6389</v>
+        <v>0.8466</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0301</v>
+        <v>0.1461</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1176</v>
+        <v>1.4809</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1176</v>
+        <v>1.9661</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.4852</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1176</v>
+        <v>1.9661</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1176</v>
+        <v>1.9661</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.4852</v>
       </c>
       <c r="K33" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1176</v>
+        <v>1.4809</v>
       </c>
       <c r="N33" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0178</v>
+        <v>1.4545</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5819</v>
+        <v>0.8315</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0102</v>
+        <v>0.1356</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0178</v>
+        <v>1.4545</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0178</v>
+        <v>1.4545</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.0178</v>
+        <v>1.4545</v>
       </c>
       <c r="I34" t="n">
-        <v>2.0178</v>
+        <v>1.4545</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L34" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0178</v>
+        <v>1.4545</v>
       </c>
       <c r="N34" t="n">
-        <v>192</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9409</v>
+        <v>1.4515</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5379</v>
+        <v>0.8298</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0413</v>
+        <v>0.1344</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9409</v>
+        <v>1.4515</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9409</v>
+        <v>1.064</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.3875</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9409</v>
+        <v>1.064</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9409</v>
+        <v>1.064</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.3875</v>
       </c>
       <c r="K35" t="n">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9409</v>
+        <v>1.4515</v>
       </c>
       <c r="N35" t="n">
-        <v>92</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>somebody</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8962</v>
+        <v>1.444</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5124</v>
+        <v>0.8255</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0593</v>
+        <v>0.1314</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8962</v>
+        <v>1.444</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8962</v>
+        <v>1.444</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8962</v>
+        <v>1.444</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8962</v>
+        <v>1.444</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8962</v>
+        <v>1.444</v>
       </c>
       <c r="N36" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.885</v>
+        <v>1.4354</v>
       </c>
       <c r="C37" t="n">
-        <v>0.506</v>
+        <v>0.8206</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0638</v>
+        <v>0.128</v>
       </c>
       <c r="E37" t="n">
-        <v>0.885</v>
+        <v>1.4354</v>
       </c>
       <c r="F37" t="n">
-        <v>0.885</v>
+        <v>1.396</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.0394</v>
       </c>
       <c r="H37" t="n">
-        <v>0.885</v>
+        <v>1.396</v>
       </c>
       <c r="I37" t="n">
-        <v>0.885</v>
+        <v>1.396</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.0394</v>
       </c>
       <c r="K37" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M37" t="n">
-        <v>0.885</v>
+        <v>1.4354</v>
       </c>
       <c r="N37" t="n">
-        <v>121</v>
+        <v>183</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>XigN</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.863</v>
+        <v>1.2373</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4934</v>
+        <v>0.7074</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0727</v>
+        <v>0.049</v>
       </c>
       <c r="E38" t="n">
-        <v>0.863</v>
+        <v>1.2373</v>
       </c>
       <c r="F38" t="n">
-        <v>0.863</v>
+        <v>1.2373</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.863</v>
+        <v>1.2373</v>
       </c>
       <c r="I38" t="n">
-        <v>0.863</v>
+        <v>1.2373</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.863</v>
+        <v>1.2373</v>
       </c>
       <c r="N38" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>XigN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.849</v>
+        <v>1.123</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4854</v>
+        <v>0.642</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0784</v>
+        <v>0.0035</v>
       </c>
       <c r="E39" t="n">
-        <v>0.849</v>
+        <v>1.123</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3342</v>
+        <v>1.123</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.4852</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.3342</v>
+        <v>1.123</v>
       </c>
       <c r="I39" t="n">
-        <v>1.3342</v>
+        <v>1.123</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4852</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="L39" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.849</v>
+        <v>1.123</v>
       </c>
       <c r="N39" t="n">
-        <v>192</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7943</v>
+        <v>0.9409</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4541</v>
+        <v>0.5379</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1005</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7943</v>
+        <v>0.9409</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2885</v>
+        <v>0.9409</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.4942</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2885</v>
+        <v>0.9409</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2885</v>
+        <v>0.9409</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.4942</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="L40" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.7943</v>
+        <v>0.9409</v>
       </c>
       <c r="N40" t="n">
-        <v>183</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7788</v>
+        <v>0.9243</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4452</v>
+        <v>0.5284</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1067</v>
+        <v>-0.0757</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7788</v>
+        <v>0.9243</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7788</v>
+        <v>1.4185</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-0.4942</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7788</v>
+        <v>1.4185</v>
       </c>
       <c r="I41" t="n">
-        <v>0.7788</v>
+        <v>1.4185</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-0.4942</v>
       </c>
       <c r="K41" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7788</v>
+        <v>0.9243000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>112</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>somebody</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6899</v>
+        <v>0.8962</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3944</v>
+        <v>0.5124</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1427</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6899</v>
+        <v>0.8962</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6899</v>
+        <v>0.8962</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.6899</v>
+        <v>0.8962</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6899</v>
+        <v>0.8962</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.6899</v>
+        <v>0.8962</v>
       </c>
       <c r="N42" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6334</v>
+        <v>0.7839</v>
       </c>
       <c r="C43" t="n">
-        <v>0.3621</v>
+        <v>0.4482</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1655</v>
+        <v>-0.1316</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6334</v>
+        <v>0.7839</v>
       </c>
       <c r="F43" t="n">
-        <v>1.4218</v>
+        <v>0.7839</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.7884</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.4218</v>
+        <v>0.7839</v>
       </c>
       <c r="I43" t="n">
-        <v>1.4218</v>
+        <v>0.7839</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.7884</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L43" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.6334</v>
+        <v>0.7839</v>
       </c>
       <c r="N43" t="n">
-        <v>188</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5069</v>
+        <v>0.7788</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2898</v>
+        <v>0.4452</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2166</v>
+        <v>-0.1336</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5069</v>
+        <v>0.7788</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5085</v>
+        <v>0.7788</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.0016</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5085</v>
+        <v>0.7788</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5085</v>
+        <v>0.7788</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.0016</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="L44" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.5068999999999999</v>
+        <v>0.7788</v>
       </c>
       <c r="N44" t="n">
-        <v>196</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.3077</v>
+        <v>0.6623</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1759</v>
+        <v>0.3786</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2971</v>
+        <v>-0.18</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3077</v>
+        <v>0.6623</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3077</v>
+        <v>1.4507</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-0.7884</v>
       </c>
       <c r="H45" t="n">
-        <v>0.3077</v>
+        <v>1.4507</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3077</v>
+        <v>1.4507</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>-0.7884</v>
       </c>
       <c r="K45" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3077</v>
+        <v>0.6623000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>120</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1535</v>
+        <v>0.5069</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0878</v>
+        <v>0.2898</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3594</v>
+        <v>-0.242</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1535</v>
+        <v>0.5069</v>
       </c>
       <c r="F46" t="n">
-        <v>1.0572</v>
+        <v>0.5085</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.0016</v>
       </c>
       <c r="H46" t="n">
-        <v>1.0572</v>
+        <v>0.5085</v>
       </c>
       <c r="I46" t="n">
-        <v>1.0572</v>
+        <v>0.5085</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.0016</v>
       </c>
       <c r="K46" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="L46" t="n">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1535</v>
+        <v>0.5068999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>183</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.1203</v>
+        <v>0.4996</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0688</v>
+        <v>0.2856</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3728</v>
+        <v>-0.2449</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1203</v>
+        <v>0.4996</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1203</v>
+        <v>1.0543</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.5547</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1203</v>
+        <v>1.0543</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1203</v>
+        <v>1.0543</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-0.5547</v>
       </c>
       <c r="K47" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1203</v>
+        <v>0.4996</v>
       </c>
       <c r="N47" t="n">
-        <v>112</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.0581</v>
+        <v>0.4306</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0332</v>
+        <v>0.2462</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3979</v>
+        <v>-0.2724</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0581</v>
+        <v>0.4306</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1746</v>
+        <v>1.3343</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.1165</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1746</v>
+        <v>1.3343</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1746</v>
+        <v>1.3343</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.1165</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="L48" t="n">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0581</v>
+        <v>0.4306000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>313</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>HSK</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0154</v>
+        <v>0.2765</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.1581</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4276</v>
+        <v>-0.3338</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0154</v>
+        <v>0.2765</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.0154</v>
+        <v>0.2765</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.0154</v>
+        <v>0.2765</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0154</v>
+        <v>0.2765</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0154</v>
+        <v>0.2765</v>
       </c>
       <c r="N49" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HSK</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.0169</v>
+        <v>0.1715</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0097</v>
+        <v>0.098</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4282</v>
+        <v>-0.3756</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.0169</v>
+        <v>0.1715</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.0169</v>
+        <v>0.1715</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.0169</v>
+        <v>0.1715</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0169</v>
+        <v>0.1715</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.0169</v>
+        <v>0.1715</v>
       </c>
       <c r="N50" t="n">
-        <v>105</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1034</v>
+        <v>0.165</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0591</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4631</v>
+        <v>-0.3782</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1034</v>
+        <v>0.165</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4513</v>
+        <v>0.165</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.5547</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4513</v>
+        <v>0.165</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4513</v>
+        <v>0.165</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.5547</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="L51" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1034</v>
+        <v>0.165</v>
       </c>
       <c r="N51" t="n">
-        <v>188</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1352</v>
+        <v>0.1021</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.0584</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.476</v>
+        <v>-0.4032</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1352</v>
+        <v>0.1021</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1352</v>
+        <v>0.1021</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1352</v>
+        <v>0.1021</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1352</v>
+        <v>0.1021</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1352</v>
+        <v>0.1021</v>
       </c>
       <c r="N52" t="n">
         <v>121</v>
@@ -2838,78 +2838,78 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.1471</v>
+        <v>0.0581</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.08409999999999999</v>
+        <v>0.0332</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4808</v>
+        <v>-0.4208</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1471</v>
+        <v>0.0581</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.1471</v>
+        <v>0.1746</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.1165</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1471</v>
+        <v>0.1746</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1471</v>
+        <v>0.1746</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.1165</v>
       </c>
       <c r="K53" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1471</v>
+        <v>0.0581</v>
       </c>
       <c r="N53" t="n">
-        <v>121</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.227</v>
+        <v>-0.1471</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1298</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5131</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.227</v>
+        <v>-0.1471</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.227</v>
+        <v>-0.1471</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.227</v>
+        <v>-0.1471</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.227</v>
+        <v>-0.1471</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.227</v>
+        <v>-0.1471</v>
       </c>
       <c r="N54" t="n">
         <v>121</v>
@@ -2930,32 +2930,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3332</v>
+        <v>-0.1582</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1905</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.556</v>
+        <v>-0.5069</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3332</v>
+        <v>-0.1582</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.3332</v>
+        <v>-0.1582</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.3332</v>
+        <v>-0.1582</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3332</v>
+        <v>-0.1582</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3332</v>
+        <v>-0.1582</v>
       </c>
       <c r="N55" t="n">
         <v>77</v>
@@ -2976,691 +2976,691 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>zhokiNg</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3684</v>
+        <v>-0.1873</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2106</v>
+        <v>-0.1071</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5702</v>
+        <v>-0.5185</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3684</v>
+        <v>-0.1873</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3684</v>
+        <v>-0.1873</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3684</v>
+        <v>-0.1873</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3684</v>
+        <v>-0.1873</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3684</v>
+        <v>-0.1873</v>
       </c>
       <c r="N56" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.4024</v>
+        <v>-0.315</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.2301</v>
+        <v>-0.1801</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5839</v>
+        <v>-0.5694</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4024</v>
+        <v>-0.315</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.4024</v>
+        <v>-0.315</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.4024</v>
+        <v>-0.315</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.4024</v>
+        <v>-0.315</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.4024</v>
+        <v>-0.315</v>
       </c>
       <c r="N57" t="n">
-        <v>112</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Not7</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4414</v>
+        <v>-0.3573</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2524</v>
+        <v>-0.2043</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5997</v>
+        <v>-0.5863</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4414</v>
+        <v>-0.3573</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4414</v>
+        <v>-0.3573</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4414</v>
+        <v>-0.3573</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4414</v>
+        <v>-0.3573</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>71</v>
+        <v>121</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.4414</v>
+        <v>-0.3573</v>
       </c>
       <c r="N58" t="n">
-        <v>71</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>zhokiNg</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5013</v>
+        <v>-0.3684</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2866</v>
+        <v>-0.2106</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6239</v>
+        <v>-0.5907</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5013</v>
+        <v>-0.3684</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5013</v>
+        <v>-0.3684</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5013</v>
+        <v>-0.3684</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5013</v>
+        <v>-0.3684</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5013</v>
+        <v>-0.3684</v>
       </c>
       <c r="N59" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5942</v>
+        <v>-0.4024</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3397</v>
+        <v>-0.2301</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6614</v>
+        <v>-0.6042</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5942</v>
+        <v>-0.4024</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5942</v>
+        <v>-0.4024</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5942</v>
+        <v>-0.4024</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5942</v>
+        <v>-0.4024</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5942</v>
+        <v>-0.4024</v>
       </c>
       <c r="N60" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>Not7</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6217</v>
+        <v>-0.4414</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3554</v>
+        <v>-0.2524</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6725</v>
+        <v>-0.6198</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6217</v>
+        <v>-0.4414</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3155</v>
+        <v>-0.4414</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.9372</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3155</v>
+        <v>-0.4414</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3155</v>
+        <v>-0.4414</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.9372</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="L61" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.6217</v>
+        <v>-0.4414</v>
       </c>
       <c r="N61" t="n">
-        <v>196</v>
+        <v>71</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>shuadapai</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7467</v>
+        <v>-0.6217</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4269</v>
+        <v>-0.3554</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.723</v>
+        <v>-0.6916</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7467</v>
+        <v>-0.6217</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7467</v>
+        <v>0.3155</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-0.9372</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.7467</v>
+        <v>0.3155</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7467</v>
+        <v>0.3155</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-0.9372</v>
       </c>
       <c r="K62" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7467</v>
+        <v>-0.6217</v>
       </c>
       <c r="N62" t="n">
-        <v>71</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>shuadapai</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7507</v>
+        <v>-0.7467</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4292</v>
+        <v>-0.4269</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7246</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7507</v>
+        <v>-0.7467</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3677</v>
+        <v>-0.7467</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3677</v>
+        <v>-0.7467</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3677</v>
+        <v>-0.7467</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>119</v>
+        <v>71</v>
       </c>
       <c r="L63" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.7507</v>
+        <v>-0.7467</v>
       </c>
       <c r="N63" t="n">
-        <v>313</v>
+        <v>71</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>forget</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7826</v>
+        <v>-0.7507</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4474</v>
+        <v>-0.4292</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7375</v>
+        <v>-0.743</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7826</v>
+        <v>-0.7507</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7826</v>
+        <v>-0.3677</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>-0.383</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7826</v>
+        <v>-0.3677</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7826</v>
+        <v>-0.3677</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>-0.383</v>
       </c>
       <c r="K64" t="n">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7826</v>
+        <v>-0.7507</v>
       </c>
       <c r="N64" t="n">
-        <v>71</v>
+        <v>313</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>forget</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7965</v>
+        <v>-0.7826</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4554</v>
+        <v>-0.4474</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7431</v>
+        <v>-0.7557</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7965</v>
+        <v>-0.7826</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.7965</v>
+        <v>-0.7826</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.7965</v>
+        <v>-0.7826</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.7965</v>
+        <v>-0.7826</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.7965</v>
+        <v>-0.7826</v>
       </c>
       <c r="N65" t="n">
-        <v>112</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HZ</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8788</v>
+        <v>-0.7965</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5024</v>
+        <v>-0.4554</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7764</v>
+        <v>-0.7612</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8788</v>
+        <v>-0.7965</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8788</v>
+        <v>-0.7965</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8788</v>
+        <v>-0.7965</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8788</v>
+        <v>-0.7965</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.8788</v>
+        <v>-0.7965</v>
       </c>
       <c r="N66" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>HZ</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8925</v>
+        <v>-0.8788</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.5102</v>
+        <v>-0.5024</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7819</v>
+        <v>-0.794</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8925</v>
+        <v>-0.8788</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.7651</v>
+        <v>-0.8788</v>
       </c>
       <c r="G67" t="n">
-        <v>0.8726</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.7651</v>
+        <v>-0.8788</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.7651</v>
+        <v>-0.8788</v>
       </c>
       <c r="J67" t="n">
-        <v>0.8726</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="L67" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.8924999999999998</v>
+        <v>-0.8788</v>
       </c>
       <c r="N67" t="n">
-        <v>241</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>captainMo</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.9923</v>
+        <v>-0.8925</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5673</v>
+        <v>-0.5102</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8222</v>
+        <v>-0.7995</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.9923</v>
+        <v>-0.8925</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.9923</v>
+        <v>-1.7651</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>0.8726</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.9923</v>
+        <v>-1.7651</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.9923</v>
+        <v>-1.7651</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>0.8726</v>
       </c>
       <c r="K68" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.9923</v>
+        <v>-0.8924999999999998</v>
       </c>
       <c r="N68" t="n">
-        <v>92</v>
+        <v>241</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>captainMo</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.0018</v>
+        <v>-0.9923</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5727</v>
+        <v>-0.5673</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.0018</v>
+        <v>-0.9923</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1279</v>
+        <v>-0.9923</v>
       </c>
       <c r="G69" t="n">
-        <v>0.1261</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1279</v>
+        <v>-0.9923</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1279</v>
+        <v>-0.9923</v>
       </c>
       <c r="J69" t="n">
-        <v>0.1261</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="L69" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.0018</v>
+        <v>-0.9923</v>
       </c>
       <c r="N69" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0606</v>
+        <v>-1.0018</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.5727</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8498</v>
+        <v>-0.843</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0606</v>
+        <v>-1.0018</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.0606</v>
+        <v>-1.1279</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>0.1261</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.0606</v>
+        <v>-1.1279</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.0606</v>
+        <v>-1.1279</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>0.1261</v>
       </c>
       <c r="K70" t="n">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.0606</v>
+        <v>-1.0018</v>
       </c>
       <c r="N70" t="n">
-        <v>77</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71">
@@ -3676,7 +3676,7 @@
         <v>-0.6148</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8558</v>
+        <v>-0.8723</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0754</v>
@@ -3722,7 +3722,7 @@
         <v>-0.6879999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9075</v>
+        <v>-0.9233</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2034</v>
@@ -3768,7 +3768,7 @@
         <v>-0.6906</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9094</v>
+        <v>-0.9252</v>
       </c>
       <c r="E73" t="n">
         <v>-1.208</v>
@@ -3814,7 +3814,7 @@
         <v>-0.7314000000000001</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9382</v>
+        <v>-0.9536</v>
       </c>
       <c r="E74" t="n">
         <v>-1.2793</v>
@@ -3860,7 +3860,7 @@
         <v>-0.8255</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0047</v>
+        <v>-1.0192</v>
       </c>
       <c r="E75" t="n">
         <v>-1.4439</v>
@@ -3906,7 +3906,7 @@
         <v>-0.853</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0241</v>
+        <v>-1.0384</v>
       </c>
       <c r="E76" t="n">
         <v>-1.4921</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>rindA</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.5774</v>
+        <v>-1.5265</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.9018</v>
+        <v>-0.8727</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0586</v>
+        <v>-1.0521</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.5774</v>
+        <v>-1.5265</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.5774</v>
+        <v>-1.5265</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.5774</v>
+        <v>-1.5265</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.5774</v>
+        <v>-1.5265</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.5774</v>
+        <v>-1.5265</v>
       </c>
       <c r="N77" t="n">
-        <v>105</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>rindA</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.8057</v>
+        <v>-1.5774</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.0323</v>
+        <v>-0.9018</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1508</v>
+        <v>-1.0723</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.8057</v>
+        <v>-1.5774</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.8057</v>
+        <v>-1.5774</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.8057</v>
+        <v>-1.5774</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.8057</v>
+        <v>-1.5774</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.8057</v>
+        <v>-1.5774</v>
       </c>
       <c r="N78" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="79">
@@ -4044,7 +4044,7 @@
         <v>-1.0933</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1939</v>
+        <v>-1.2058</v>
       </c>
       <c r="E79" t="n">
         <v>-1.9124</v>
@@ -4090,7 +4090,7 @@
         <v>-1.1034</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.2011</v>
+        <v>-1.2129</v>
       </c>
       <c r="E80" t="n">
         <v>-1.9301</v>
@@ -4136,7 +4136,7 @@
         <v>-1.2221</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.2849</v>
+        <v>-1.2955</v>
       </c>
       <c r="E81" t="n">
         <v>-2.1376</v>
